--- a/numerical-workflows/v2/framework/06_最终配置/爬塔/TowerFirstReward.xlsx
+++ b/numerical-workflows/v2/framework/06_最终配置/爬塔/TowerFirstReward.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="中文说明" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中文说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.375" customWidth="1" min="4" max="4"/>
@@ -653,7 +653,7 @@
         <v>24000010</v>
       </c>
       <c r="E14" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15">
@@ -769,7 +769,7 @@
         <v>24000020</v>
       </c>
       <c r="E24" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
@@ -885,7 +885,7 @@
         <v>24000030</v>
       </c>
       <c r="E34" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="35">
@@ -1697,6 +1697,1166 @@
         <v>24000100</v>
       </c>
       <c r="E104" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="n">
+        <v>101</v>
+      </c>
+      <c r="C105" t="n">
+        <v>101</v>
+      </c>
+      <c r="D105" t="n">
+        <v>24000101</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="n">
+        <v>102</v>
+      </c>
+      <c r="C106" t="n">
+        <v>102</v>
+      </c>
+      <c r="D106" t="n">
+        <v>24000102</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="n">
+        <v>103</v>
+      </c>
+      <c r="C107" t="n">
+        <v>103</v>
+      </c>
+      <c r="D107" t="n">
+        <v>24000103</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="n">
+        <v>104</v>
+      </c>
+      <c r="C108" t="n">
+        <v>104</v>
+      </c>
+      <c r="D108" t="n">
+        <v>24000104</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="n">
+        <v>105</v>
+      </c>
+      <c r="C109" t="n">
+        <v>105</v>
+      </c>
+      <c r="D109" t="n">
+        <v>24000105</v>
+      </c>
+      <c r="E109" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="n">
+        <v>106</v>
+      </c>
+      <c r="C110" t="n">
+        <v>106</v>
+      </c>
+      <c r="D110" t="n">
+        <v>24000106</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" t="n">
+        <v>107</v>
+      </c>
+      <c r="C111" t="n">
+        <v>107</v>
+      </c>
+      <c r="D111" t="n">
+        <v>24000107</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" t="n">
+        <v>108</v>
+      </c>
+      <c r="C112" t="n">
+        <v>108</v>
+      </c>
+      <c r="D112" t="n">
+        <v>24000108</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" t="n">
+        <v>109</v>
+      </c>
+      <c r="C113" t="n">
+        <v>109</v>
+      </c>
+      <c r="D113" t="n">
+        <v>24000109</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" t="n">
+        <v>110</v>
+      </c>
+      <c r="C114" t="n">
+        <v>110</v>
+      </c>
+      <c r="D114" t="n">
+        <v>24000110</v>
+      </c>
+      <c r="E114" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" t="n">
+        <v>111</v>
+      </c>
+      <c r="C115" t="n">
+        <v>111</v>
+      </c>
+      <c r="D115" t="n">
+        <v>24000111</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" t="n">
+        <v>112</v>
+      </c>
+      <c r="C116" t="n">
+        <v>112</v>
+      </c>
+      <c r="D116" t="n">
+        <v>24000112</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" t="n">
+        <v>113</v>
+      </c>
+      <c r="C117" t="n">
+        <v>113</v>
+      </c>
+      <c r="D117" t="n">
+        <v>24000113</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" t="n">
+        <v>114</v>
+      </c>
+      <c r="C118" t="n">
+        <v>114</v>
+      </c>
+      <c r="D118" t="n">
+        <v>24000114</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" t="n">
+        <v>115</v>
+      </c>
+      <c r="C119" t="n">
+        <v>115</v>
+      </c>
+      <c r="D119" t="n">
+        <v>24000115</v>
+      </c>
+      <c r="E119" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" t="n">
+        <v>116</v>
+      </c>
+      <c r="C120" t="n">
+        <v>116</v>
+      </c>
+      <c r="D120" t="n">
+        <v>24000116</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" t="n">
+        <v>117</v>
+      </c>
+      <c r="C121" t="n">
+        <v>117</v>
+      </c>
+      <c r="D121" t="n">
+        <v>24000117</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" t="n">
+        <v>118</v>
+      </c>
+      <c r="C122" t="n">
+        <v>118</v>
+      </c>
+      <c r="D122" t="n">
+        <v>24000118</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" t="n">
+        <v>119</v>
+      </c>
+      <c r="C123" t="n">
+        <v>119</v>
+      </c>
+      <c r="D123" t="n">
+        <v>24000119</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" t="n">
+        <v>120</v>
+      </c>
+      <c r="C124" t="n">
+        <v>120</v>
+      </c>
+      <c r="D124" t="n">
+        <v>24000120</v>
+      </c>
+      <c r="E124" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" t="n">
+        <v>121</v>
+      </c>
+      <c r="C125" t="n">
+        <v>121</v>
+      </c>
+      <c r="D125" t="n">
+        <v>24000121</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" t="n">
+        <v>122</v>
+      </c>
+      <c r="C126" t="n">
+        <v>122</v>
+      </c>
+      <c r="D126" t="n">
+        <v>24000122</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" t="n">
+        <v>123</v>
+      </c>
+      <c r="C127" t="n">
+        <v>123</v>
+      </c>
+      <c r="D127" t="n">
+        <v>24000123</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="n">
+        <v>124</v>
+      </c>
+      <c r="C128" t="n">
+        <v>124</v>
+      </c>
+      <c r="D128" t="n">
+        <v>24000124</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="n">
+        <v>125</v>
+      </c>
+      <c r="C129" t="n">
+        <v>125</v>
+      </c>
+      <c r="D129" t="n">
+        <v>24000125</v>
+      </c>
+      <c r="E129" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="n">
+        <v>126</v>
+      </c>
+      <c r="C130" t="n">
+        <v>126</v>
+      </c>
+      <c r="D130" t="n">
+        <v>24000126</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="n">
+        <v>127</v>
+      </c>
+      <c r="C131" t="n">
+        <v>127</v>
+      </c>
+      <c r="D131" t="n">
+        <v>24000127</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="n">
+        <v>128</v>
+      </c>
+      <c r="C132" t="n">
+        <v>128</v>
+      </c>
+      <c r="D132" t="n">
+        <v>24000128</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="n">
+        <v>129</v>
+      </c>
+      <c r="C133" t="n">
+        <v>129</v>
+      </c>
+      <c r="D133" t="n">
+        <v>24000129</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="n">
+        <v>130</v>
+      </c>
+      <c r="C134" t="n">
+        <v>130</v>
+      </c>
+      <c r="D134" t="n">
+        <v>24000130</v>
+      </c>
+      <c r="E134" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="n">
+        <v>131</v>
+      </c>
+      <c r="C135" t="n">
+        <v>131</v>
+      </c>
+      <c r="D135" t="n">
+        <v>24000131</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" t="n">
+        <v>132</v>
+      </c>
+      <c r="C136" t="n">
+        <v>132</v>
+      </c>
+      <c r="D136" t="n">
+        <v>24000132</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" t="n">
+        <v>133</v>
+      </c>
+      <c r="C137" t="n">
+        <v>133</v>
+      </c>
+      <c r="D137" t="n">
+        <v>24000133</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" t="n">
+        <v>134</v>
+      </c>
+      <c r="C138" t="n">
+        <v>134</v>
+      </c>
+      <c r="D138" t="n">
+        <v>24000134</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" t="n">
+        <v>135</v>
+      </c>
+      <c r="C139" t="n">
+        <v>135</v>
+      </c>
+      <c r="D139" t="n">
+        <v>24000135</v>
+      </c>
+      <c r="E139" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" t="n">
+        <v>136</v>
+      </c>
+      <c r="C140" t="n">
+        <v>136</v>
+      </c>
+      <c r="D140" t="n">
+        <v>24000136</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" t="n">
+        <v>137</v>
+      </c>
+      <c r="C141" t="n">
+        <v>137</v>
+      </c>
+      <c r="D141" t="n">
+        <v>24000137</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" t="n">
+        <v>138</v>
+      </c>
+      <c r="C142" t="n">
+        <v>138</v>
+      </c>
+      <c r="D142" t="n">
+        <v>24000138</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="n">
+        <v>139</v>
+      </c>
+      <c r="C143" t="n">
+        <v>139</v>
+      </c>
+      <c r="D143" t="n">
+        <v>24000139</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" t="n">
+        <v>140</v>
+      </c>
+      <c r="C144" t="n">
+        <v>140</v>
+      </c>
+      <c r="D144" t="n">
+        <v>24000140</v>
+      </c>
+      <c r="E144" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" t="n">
+        <v>141</v>
+      </c>
+      <c r="C145" t="n">
+        <v>141</v>
+      </c>
+      <c r="D145" t="n">
+        <v>24000141</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" t="n">
+        <v>142</v>
+      </c>
+      <c r="C146" t="n">
+        <v>142</v>
+      </c>
+      <c r="D146" t="n">
+        <v>24000142</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" t="n">
+        <v>143</v>
+      </c>
+      <c r="C147" t="n">
+        <v>143</v>
+      </c>
+      <c r="D147" t="n">
+        <v>24000143</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" t="n">
+        <v>144</v>
+      </c>
+      <c r="C148" t="n">
+        <v>144</v>
+      </c>
+      <c r="D148" t="n">
+        <v>24000144</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" t="n">
+        <v>145</v>
+      </c>
+      <c r="C149" t="n">
+        <v>145</v>
+      </c>
+      <c r="D149" t="n">
+        <v>24000145</v>
+      </c>
+      <c r="E149" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" t="n">
+        <v>146</v>
+      </c>
+      <c r="C150" t="n">
+        <v>146</v>
+      </c>
+      <c r="D150" t="n">
+        <v>24000146</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" t="n">
+        <v>147</v>
+      </c>
+      <c r="C151" t="n">
+        <v>147</v>
+      </c>
+      <c r="D151" t="n">
+        <v>24000147</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" t="n">
+        <v>148</v>
+      </c>
+      <c r="C152" t="n">
+        <v>148</v>
+      </c>
+      <c r="D152" t="n">
+        <v>24000148</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" t="n">
+        <v>149</v>
+      </c>
+      <c r="C153" t="n">
+        <v>149</v>
+      </c>
+      <c r="D153" t="n">
+        <v>24000149</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" t="n">
+        <v>150</v>
+      </c>
+      <c r="C154" t="n">
+        <v>150</v>
+      </c>
+      <c r="D154" t="n">
+        <v>24000150</v>
+      </c>
+      <c r="E154" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" t="n">
+        <v>151</v>
+      </c>
+      <c r="C155" t="n">
+        <v>151</v>
+      </c>
+      <c r="D155" t="n">
+        <v>24000151</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" t="n">
+        <v>152</v>
+      </c>
+      <c r="C156" t="n">
+        <v>152</v>
+      </c>
+      <c r="D156" t="n">
+        <v>24000152</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="B157" t="n">
+        <v>153</v>
+      </c>
+      <c r="C157" t="n">
+        <v>153</v>
+      </c>
+      <c r="D157" t="n">
+        <v>24000153</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="B158" t="n">
+        <v>154</v>
+      </c>
+      <c r="C158" t="n">
+        <v>154</v>
+      </c>
+      <c r="D158" t="n">
+        <v>24000154</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="B159" t="n">
+        <v>155</v>
+      </c>
+      <c r="C159" t="n">
+        <v>155</v>
+      </c>
+      <c r="D159" t="n">
+        <v>24000155</v>
+      </c>
+      <c r="E159" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="B160" t="n">
+        <v>156</v>
+      </c>
+      <c r="C160" t="n">
+        <v>156</v>
+      </c>
+      <c r="D160" t="n">
+        <v>24000156</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="B161" t="n">
+        <v>157</v>
+      </c>
+      <c r="C161" t="n">
+        <v>157</v>
+      </c>
+      <c r="D161" t="n">
+        <v>24000157</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" t="n">
+        <v>158</v>
+      </c>
+      <c r="C162" t="n">
+        <v>158</v>
+      </c>
+      <c r="D162" t="n">
+        <v>24000158</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="n">
+        <v>159</v>
+      </c>
+      <c r="C163" t="n">
+        <v>159</v>
+      </c>
+      <c r="D163" t="n">
+        <v>24000159</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="n">
+        <v>160</v>
+      </c>
+      <c r="C164" t="n">
+        <v>160</v>
+      </c>
+      <c r="D164" t="n">
+        <v>24000160</v>
+      </c>
+      <c r="E164" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="B165" t="n">
+        <v>161</v>
+      </c>
+      <c r="C165" t="n">
+        <v>161</v>
+      </c>
+      <c r="D165" t="n">
+        <v>24000161</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="B166" t="n">
+        <v>162</v>
+      </c>
+      <c r="C166" t="n">
+        <v>162</v>
+      </c>
+      <c r="D166" t="n">
+        <v>24000162</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="B167" t="n">
+        <v>163</v>
+      </c>
+      <c r="C167" t="n">
+        <v>163</v>
+      </c>
+      <c r="D167" t="n">
+        <v>24000163</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="B168" t="n">
+        <v>164</v>
+      </c>
+      <c r="C168" t="n">
+        <v>164</v>
+      </c>
+      <c r="D168" t="n">
+        <v>24000164</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="B169" t="n">
+        <v>165</v>
+      </c>
+      <c r="C169" t="n">
+        <v>165</v>
+      </c>
+      <c r="D169" t="n">
+        <v>24000165</v>
+      </c>
+      <c r="E169" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="B170" t="n">
+        <v>166</v>
+      </c>
+      <c r="C170" t="n">
+        <v>166</v>
+      </c>
+      <c r="D170" t="n">
+        <v>24000166</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="B171" t="n">
+        <v>167</v>
+      </c>
+      <c r="C171" t="n">
+        <v>167</v>
+      </c>
+      <c r="D171" t="n">
+        <v>24000167</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="B172" t="n">
+        <v>168</v>
+      </c>
+      <c r="C172" t="n">
+        <v>168</v>
+      </c>
+      <c r="D172" t="n">
+        <v>24000168</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="B173" t="n">
+        <v>169</v>
+      </c>
+      <c r="C173" t="n">
+        <v>169</v>
+      </c>
+      <c r="D173" t="n">
+        <v>24000169</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="B174" t="n">
+        <v>170</v>
+      </c>
+      <c r="C174" t="n">
+        <v>170</v>
+      </c>
+      <c r="D174" t="n">
+        <v>24000170</v>
+      </c>
+      <c r="E174" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="B175" t="n">
+        <v>171</v>
+      </c>
+      <c r="C175" t="n">
+        <v>171</v>
+      </c>
+      <c r="D175" t="n">
+        <v>24000171</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="B176" t="n">
+        <v>172</v>
+      </c>
+      <c r="C176" t="n">
+        <v>172</v>
+      </c>
+      <c r="D176" t="n">
+        <v>24000172</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="B177" t="n">
+        <v>173</v>
+      </c>
+      <c r="C177" t="n">
+        <v>173</v>
+      </c>
+      <c r="D177" t="n">
+        <v>24000173</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="B178" t="n">
+        <v>174</v>
+      </c>
+      <c r="C178" t="n">
+        <v>174</v>
+      </c>
+      <c r="D178" t="n">
+        <v>24000174</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="B179" t="n">
+        <v>175</v>
+      </c>
+      <c r="C179" t="n">
+        <v>175</v>
+      </c>
+      <c r="D179" t="n">
+        <v>24000175</v>
+      </c>
+      <c r="E179" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="B180" t="n">
+        <v>176</v>
+      </c>
+      <c r="C180" t="n">
+        <v>176</v>
+      </c>
+      <c r="D180" t="n">
+        <v>24000176</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="B181" t="n">
+        <v>177</v>
+      </c>
+      <c r="C181" t="n">
+        <v>177</v>
+      </c>
+      <c r="D181" t="n">
+        <v>24000177</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="B182" t="n">
+        <v>178</v>
+      </c>
+      <c r="C182" t="n">
+        <v>178</v>
+      </c>
+      <c r="D182" t="n">
+        <v>24000178</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="B183" t="n">
+        <v>179</v>
+      </c>
+      <c r="C183" t="n">
+        <v>179</v>
+      </c>
+      <c r="D183" t="n">
+        <v>24000179</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="B184" t="n">
+        <v>180</v>
+      </c>
+      <c r="C184" t="n">
+        <v>180</v>
+      </c>
+      <c r="D184" t="n">
+        <v>24000180</v>
+      </c>
+      <c r="E184" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="B185" t="n">
+        <v>181</v>
+      </c>
+      <c r="C185" t="n">
+        <v>181</v>
+      </c>
+      <c r="D185" t="n">
+        <v>24000181</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="B186" t="n">
+        <v>182</v>
+      </c>
+      <c r="C186" t="n">
+        <v>182</v>
+      </c>
+      <c r="D186" t="n">
+        <v>24000182</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="B187" t="n">
+        <v>183</v>
+      </c>
+      <c r="C187" t="n">
+        <v>183</v>
+      </c>
+      <c r="D187" t="n">
+        <v>24000183</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="B188" t="n">
+        <v>184</v>
+      </c>
+      <c r="C188" t="n">
+        <v>184</v>
+      </c>
+      <c r="D188" t="n">
+        <v>24000184</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="B189" t="n">
+        <v>185</v>
+      </c>
+      <c r="C189" t="n">
+        <v>185</v>
+      </c>
+      <c r="D189" t="n">
+        <v>24000185</v>
+      </c>
+      <c r="E189" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="B190" t="n">
+        <v>186</v>
+      </c>
+      <c r="C190" t="n">
+        <v>186</v>
+      </c>
+      <c r="D190" t="n">
+        <v>24000186</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="B191" t="n">
+        <v>187</v>
+      </c>
+      <c r="C191" t="n">
+        <v>187</v>
+      </c>
+      <c r="D191" t="n">
+        <v>24000187</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="B192" t="n">
+        <v>188</v>
+      </c>
+      <c r="C192" t="n">
+        <v>188</v>
+      </c>
+      <c r="D192" t="n">
+        <v>24000188</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="B193" t="n">
+        <v>189</v>
+      </c>
+      <c r="C193" t="n">
+        <v>189</v>
+      </c>
+      <c r="D193" t="n">
+        <v>24000189</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="B194" t="n">
+        <v>190</v>
+      </c>
+      <c r="C194" t="n">
+        <v>190</v>
+      </c>
+      <c r="D194" t="n">
+        <v>24000190</v>
+      </c>
+      <c r="E194" t="n">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="B195" t="n">
+        <v>191</v>
+      </c>
+      <c r="C195" t="n">
+        <v>191</v>
+      </c>
+      <c r="D195" t="n">
+        <v>24000191</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="B196" t="n">
+        <v>192</v>
+      </c>
+      <c r="C196" t="n">
+        <v>192</v>
+      </c>
+      <c r="D196" t="n">
+        <v>24000192</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="B197" t="n">
+        <v>193</v>
+      </c>
+      <c r="C197" t="n">
+        <v>193</v>
+      </c>
+      <c r="D197" t="n">
+        <v>24000193</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="B198" t="n">
+        <v>194</v>
+      </c>
+      <c r="C198" t="n">
+        <v>194</v>
+      </c>
+      <c r="D198" t="n">
+        <v>24000194</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="B199" t="n">
+        <v>195</v>
+      </c>
+      <c r="C199" t="n">
+        <v>195</v>
+      </c>
+      <c r="D199" t="n">
+        <v>24000195</v>
+      </c>
+      <c r="E199" t="n">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="B200" t="n">
+        <v>196</v>
+      </c>
+      <c r="C200" t="n">
+        <v>196</v>
+      </c>
+      <c r="D200" t="n">
+        <v>24000196</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="B201" t="n">
+        <v>197</v>
+      </c>
+      <c r="C201" t="n">
+        <v>197</v>
+      </c>
+      <c r="D201" t="n">
+        <v>24000197</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="B202" t="n">
+        <v>198</v>
+      </c>
+      <c r="C202" t="n">
+        <v>198</v>
+      </c>
+      <c r="D202" t="n">
+        <v>24000198</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="B203" t="n">
+        <v>199</v>
+      </c>
+      <c r="C203" t="n">
+        <v>199</v>
+      </c>
+      <c r="D203" t="n">
+        <v>24000199</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="B204" t="n">
+        <v>200</v>
+      </c>
+      <c r="C204" t="n">
+        <v>200</v>
+      </c>
+      <c r="D204" t="n">
+        <v>24000200</v>
+      </c>
+      <c r="E204" t="n">
         <v>103</v>
       </c>
     </row>
@@ -1750,7 +2910,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TOWER-20260729-F01</t>
+          <t>TOWER-20260904-F02</t>
         </is>
       </c>
     </row>
@@ -1762,7 +2922,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VALUE_READY_REFERENCE_CHG041</t>
+          <t>VALUE_READY_REFERENCE_CHG043</t>
         </is>
       </c>
     </row>
@@ -1798,7 +2958,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1-100层继续引用DropId 24000001-24000100；尾数5层展示旅券106，整10层展示熔晶103。</t>
+          <t>1-100层继续引用DropId 24000001-24000100；尾数5层及10/20/30层展示旅券106，40-100整10层展示熔晶103。</t>
         </is>
       </c>
     </row>
